--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P1376_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P1376_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.5450429176300023</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6769290861434174</v>
+        <v>0.6548428386247492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4657387413642067</v>
+        <v>0.5450786136754295</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6769290861434173</v>
+        <v>0.6548428386247492</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5403673882005813</v>
+        <v>0.4548080219605209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7188791760896567</v>
+        <v>0.6051252552961927</v>
       </c>
       <c r="G2" t="n">
-        <v>0.998915148061319</v>
+        <v>0.9998113209027412</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999417524526577</v>
+        <v>0.9998531310417058</v>
       </c>
       <c r="I2" t="n">
-        <v>0.697008547008547</v>
+        <v>0.6311965811965812</v>
       </c>
     </row>
   </sheetData>
